--- a/audio_ficition/books/excel/book-zh-xiaoyuzhou.xlsx
+++ b/audio_ficition/books/excel/book-zh-xiaoyuzhou.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-07-04 16:33:26</t>
+          <t>2025-07-04 19:02:38</t>
         </is>
       </c>
     </row>
@@ -467,13 +467,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025-07-05 16:33:26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/audio_ficition/books/excel/book-zh-xiaoyuzhou.xlsx
+++ b/audio_ficition/books/excel/book-zh-xiaoyuzhou.xlsx
@@ -467,9 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-07-05 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -478,9 +482,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-07-06 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -489,9 +497,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-07-07 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -500,9 +512,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-07-08 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -511,9 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-07-09 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,9 +542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-07-10 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -533,9 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-07-11 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -544,9 +572,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-07-12 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -555,9 +587,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-07-13 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -566,9 +602,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-07-14 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -577,9 +617,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-07-15 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -588,9 +632,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -599,9 +647,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:17:56</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -610,9 +662,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:18:57</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -621,9 +677,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:21:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -632,9 +692,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:22:01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,9 +707,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:23:02</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -654,9 +722,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-07-16 19:24:03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
